--- a/1차 개발 설계서/06 검수 및 추적.xlsx
+++ b/1차 개발 설계서/06 검수 및 추적.xlsx
@@ -21,9 +21,9 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'요구사항추적'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'공통정책추적'!$A$1:$D$13</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'공통정책추적'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'기능검수'!$A$1:$M$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'기능검수'!$A$1:$M$117</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'기능검수'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'계약통합검수'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'계약통합검수'!$A$1:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'계약통합검수'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'보완개발순서'!$A$1:$D$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'보완개발순서'!$1:$1</definedName>
@@ -663,7 +663,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="51" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>F05</t>
@@ -691,7 +691,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>TC-F05-01, TC-F05-02, TC-F05-03, TC-F05-04</t>
+          <t>TC-F05-01, TC-F05-02, TC-F05-03, TC-F05-04, TC-F05-05, TC-F05-06, TC-F05-07, TC-F05-08</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>새 초대2개·재공유·여러계정 참여</t>
+          <t>방장·일반 참여자의 조회·새 발급·공유·복사·타인 발급 초대 취소</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>기존 초대 유지·만료 연장 없음·참여로 횟수 미소모</t>
+          <t>모든 현재 참여자에게 동일 권한·발급자 이력 유지</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>발급시각-1ms·만료-1ms·만료시각</t>
+          <t>비참여자·탈퇴·퇴장·이용 제한 계정의 직접 요청·이전 요청 재시도</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>발급 전/만료는 거부, 유효 구간만 허용</t>
+          <t>조회·발급·취소 모두 거부·입력/결과 경로로 권한 우회 불가</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49회에서 두 요청 동시 확인·51번째 확인·로그인 복귀 재확인</t>
+          <t>발급자 탈퇴 후 남은 참여자의 초대 관리</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50회까지 응답·소진 구분 안내·복귀는 횟수 미증가·기존 참여자 영향 없음</t>
+          <t>기존 초대의 기한·횟수·상태 유지·남은 참여자는 조회·취소 가능</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2996,7 +2996,7 @@
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>9명에서2계정 동시참여·차단·종료·취소·소진·이미참여 구분</t>
+          <t>초대 발급/취소와 참여 종료 동시 처리</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>최대10명·활성참여 하나·구분된 안내·이미참여는 인원 불변</t>
+          <t>사용자·모임 잠금과 현재 참여 재검증·참여 종료 뒤 늦은 새 발급/취소 거부</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3058,37 +3058,37 @@
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-F06-01</t>
+          <t>TC-F05-05</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>모임 달력·일정 상세</t>
+          <t>초대 발급·공유·참여</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>다일 일정 선택·전체/날짜필터·뒤로 복귀</t>
+          <t>새 초대2개·재공유·여러계정 참여</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>단일 일정 전체 상세·월/필터/스크롤 복원</t>
+          <t>기존 초대 유지·만료 연장 없음·참여로 횟수 미소모</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI08</t>
+          <t>UI23, UI24</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3113,37 +3113,37 @@
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>TC-F06-02</t>
+          <t>TC-F05-06</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>모임 달력·일정 상세</t>
+          <t>초대 발급·공유·참여</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>월요일 시작·같은날4일정·여러 날 일정의 셀 표시</t>
+          <t>발급시각-1ms·만료-1ms·만료시각</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>최대3개+나머지수·기간 모든 날짜 셀·날짜선택 전체목록</t>
+          <t>발급 전/만료는 거부, 유효 구간만 허용</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI08</t>
+          <t>UI23, UI24</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3168,37 +3168,37 @@
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-F06-03</t>
+          <t>TC-F05-07</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>모임 달력·일정 상세</t>
+          <t>초대 발급·공유·참여</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>기간 변경으로 선택필터 범위 이탈</t>
+          <t>49회에서 두 요청 동시 확인·51번째 확인·로그인 복귀 재확인</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>전체로 복귀하고 안내</t>
+          <t>50회까지 응답·소진 구분 안내·복귀는 횟수 미증가·기존 참여자 영향 없음</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI08</t>
+          <t>UI23, UI24</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3216,44 +3216,44 @@
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>TC-F06-04</t>
+          <t>TC-F05-08</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F06</t>
+          <t>F05</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>모임 달력·일정 상세</t>
+          <t>초대 발급·공유·참여</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>방문별 예정 시각·시간 미정·장소 개수 표시</t>
+          <t>9명에서2계정 동시참여·차단·종료·취소·소진·이미참여 구분</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>방문일 순서·시각 표시, 일정 자체에는 시각 없음</t>
+          <t>최대10명·활성참여 하나·구분된 안내·이미참여는 인원 불변</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI08</t>
+          <t>UI23, UI24</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3271,24 +3271,24 @@
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-F07-01</t>
+          <t>TC-F06-01</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>일정 수동 추가·기간 설정</t>
+          <t>모임 달력·일정 상세</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3298,17 +3298,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>당일·19~21일 기간 일정 수동 추가</t>
+          <t>다일 일정 선택·전체/날짜필터·뒤로 복귀</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>하나의 일정·달력 표시 일치</t>
+          <t>단일 일정 전체 상세·월/필터/스크롤 복원</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>UI04, UI05, UI06</t>
+          <t>UI05, UI08</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3326,24 +3326,24 @@
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>TC-F07-02</t>
+          <t>TC-F06-02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>일정 수동 추가·기간 설정</t>
+          <t>모임 달력·일정 상세</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -3353,17 +3353,17 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>날짜 역전·367일·제목 101자·공백 제목</t>
+          <t>월요일 시작·같은날4일정·여러 날 일정의 셀 표시</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>거부·입력 유지</t>
+          <t>최대3개+나머지수·기간 모든 날짜 셀·날짜선택 전체목록</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>UI04, UI05, UI06</t>
+          <t>UI05, UI08</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -3381,24 +3381,24 @@
       <c r="L27" s="3" t="inlineStr"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-F07-03</t>
+          <t>TC-F06-03</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>일정 수동 추가·기간 설정</t>
+          <t>모임 달력·일정 상세</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>겹치는 기간 일정 추가·응답 유실 후 같은 키 재시도</t>
+          <t>기간 변경으로 선택필터 범위 이탈</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>겹침 안내 후 허용·중복 생성 없음</t>
+          <t>전체로 복귀하고 안내</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>UI04, UI05, UI06</t>
+          <t>UI05, UI08</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3436,24 +3436,24 @@
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>TC-F07-04</t>
+          <t>TC-F06-04</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F07</t>
+          <t>F06</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>일정 수동 추가·기간 설정</t>
+          <t>모임 달력·일정 상세</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -3463,17 +3463,17 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>일반 참여자 생성·allDay/startAt/recurrence 필드 전송</t>
+          <t>방문별 예정 시각·시간 미정·장소 개수 표시</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>서버 거부·알 수 없는 필드 거부</t>
+          <t>방문일 순서·시각 표시, 일정 자체에는 시각 없음</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>UI04, UI05, UI06</t>
+          <t>UI05, UI08</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -3491,24 +3491,24 @@
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-F08-01</t>
+          <t>TC-F07-01</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>일정 변경·취소</t>
+          <t>일정 수동 추가·기간 설정</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3518,17 +3518,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>제목·기간 변경 시 기간 밖 방문/기록 영향 확인</t>
+          <t>당일·19~21일 기간 일정 수동 추가</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>개수 표시·확인 후 전체/기간밖 영역 유지·confirm 없으면 409</t>
+          <t>하나의 일정·달력 표시 일치</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI35</t>
+          <t>UI04, UI05, UI06</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3546,24 +3546,24 @@
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>TC-F08-02</t>
+          <t>TC-F07-02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>일정 변경·취소</t>
+          <t>일정 수동 추가·기간 설정</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>기간 축소 후 신규 범위밖 지정·기간 안 재지정</t>
+          <t>날짜 역전·367일·제목 101자·공백 제목</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>신규 거부·기간 안 재지정 허용</t>
+          <t>거부·입력 유지</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI35</t>
+          <t>UI04, UI05, UI06</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -3601,24 +3601,24 @@
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TC-F08-03</t>
+          <t>TC-F07-03</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>일정 변경·취소</t>
+          <t>일정 수동 추가·기간 설정</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3628,17 +3628,17 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>기록 있는 일정 취소 후 신규 접수·취소 전 접수 재시도</t>
+          <t>겹치는 기간 일정 추가·응답 유실 후 같은 키 재시도</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>신규 거부·기존 동일 파일만 완료</t>
+          <t>겹침 안내 후 허용·중복 생성 없음</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI35</t>
+          <t>UI04, UI05, UI06</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3656,24 +3656,24 @@
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TC-F08-04</t>
+          <t>TC-F07-04</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F08</t>
+          <t>F07</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>일정 변경·취소</t>
+          <t>일정 수동 추가·기간 설정</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -3683,17 +3683,17 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>동시 변경·취소 재시도·취소 일정 재활성 시도</t>
+          <t>일반 참여자 생성·allDay/startAt/recurrence 필드 전송</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>충돌 입력 유지·멱등·재활성 거부</t>
+          <t>서버 거부·알 수 없는 필드 거부</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI35</t>
+          <t>UI04, UI05, UI06</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3711,24 +3711,24 @@
       <c r="L33" s="3" t="inlineStr"/>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TC-F09-01</t>
+          <t>TC-F08-01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
+          <t>일정 변경·취소</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3738,17 +3738,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>검색→지도이동→영역검색→예정시각 입력→방문추가</t>
+          <t>제목·기간 변경 시 기간 밖 방문/기록 영향 확인</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>목록마커 연동·방문일 마지막순서·시각 저장</t>
+          <t>개수 표시·확인 후 전체/기간밖 영역 유지·confirm 없으면 409</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>UI08, UI10, UI11, UI13</t>
+          <t>UI05, UI06, UI35</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3773,17 +3773,17 @@
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>TC-F09-02</t>
+          <t>TC-F08-02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
+          <t>일정 변경·취소</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -3793,17 +3793,17 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>위치 거절·좌표없는 수기장소·시각 미입력</t>
+          <t>기간 축소 후 신규 범위밖 지정·기간 안 재지정</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>검색/등록 가능, 가짜 거리/마커 없음·시간 미정 저장</t>
+          <t>신규 거부·기간 안 재지정 허용</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>UI08, UI10, UI11, UI13</t>
+          <t>UI05, UI06, UI35</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -3828,17 +3828,17 @@
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TC-F09-03</t>
+          <t>TC-F08-03</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
+          <t>일정 변경·취소</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3848,17 +3848,17 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>동일 공급자 장소 같은날/다른날·수기6자리좌표</t>
+          <t>기록 있는 일정 취소 후 신규 접수·취소 전 접수 재시도</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>같은날 중복 거부·다른날 허용·정규화 비교</t>
+          <t>신규 거부·기존 동일 파일만 완료</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>UI08, UI10, UI11, UI13</t>
+          <t>UI05, UI06, UI35</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3883,17 +3883,17 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>TC-F09-04</t>
+          <t>TC-F08-04</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F09</t>
+          <t>F08</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
+          <t>일정 변경·취소</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3903,17 +3903,17 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>14개에서 두 사람 동시 추가·16번째 추가·빈 방문 삭제 후 추가</t>
+          <t>동시 변경·취소 재시도·취소 일정 재활성 시도</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>15개까지만 확정·VISIT_LIMIT 안내·자리 복귀</t>
+          <t>충돌 입력 유지·멱등·재활성 거부</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>UI08, UI10, UI11, UI13</t>
+          <t>UI05, UI06, UI35</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -3938,17 +3938,17 @@
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TC-F10-01</t>
+          <t>TC-F09-01</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>방문 계획 편집</t>
+          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3958,17 +3958,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>순서·동일시각·미입력·날짜제목 동시 저장</t>
+          <t>검색→지도이동→영역검색→예정시각 입력→방문추가</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>사용자 순서 유지·비운 제목은 날짜</t>
+          <t>목록마커 연동·방문일 마지막순서·시각 저장</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>UI12</t>
+          <t>UI08, UI10, UI11, UI13</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3986,24 +3986,24 @@
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>TC-F10-02</t>
+          <t>TC-F09-02</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>방문 계획 편집</t>
+          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>방문 누락·중복·다른 날짜 혼입</t>
+          <t>위치 거절·좌표없는 수기장소·시각 미입력</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>전체 저장 거부</t>
+          <t>검색/등록 가능, 가짜 거리/마커 없음·시간 미정 저장</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>UI12</t>
+          <t>UI08, UI10, UI11, UI13</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -4048,17 +4048,17 @@
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TC-F10-03</t>
+          <t>TC-F09-03</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>방문 계획 편집</t>
+          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4068,17 +4068,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>시각23:55/24:00·제목30/31자·시각순 정렬 버튼</t>
+          <t>동일 공급자 장소 같은날/다른날·수기6자리좌표</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23:55/30자만 허용·버튼 눌렀을 때만 재정렬</t>
+          <t>같은날 중복 거부·다른날 허용·정규화 비교</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>UI12</t>
+          <t>UI08, UI10, UI11, UI13</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4103,17 +4103,17 @@
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TC-F10-04</t>
+          <t>TC-F09-04</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F10</t>
+          <t>F09</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>방문 계획 편집</t>
+          <t>장소 검색·직접 등록·방문 추가 (P12)</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>동시계획 수정·미저장 이탈</t>
+          <t>14개에서 두 사람 동시 추가·16번째 추가·빈 방문 삭제 후 추가</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>먼저 저장 유지·입력 보존·저장/버리기/계속</t>
+          <t>15개까지만 확정·VISIT_LIMIT 안내·자리 복귀</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>UI12</t>
+          <t>UI08, UI10, UI11, UI13</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
@@ -4158,17 +4158,17 @@
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>TC-F11-01</t>
+          <t>TC-F10-01</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>빈 방문·빈 일정 삭제 (P05)</t>
+          <t>방문 계획 편집</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4178,17 +4178,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>빈방문·마지막빈일정 삭제</t>
+          <t>순서·동일시각·미입력·날짜제목 동시 저장</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>관련 빈 계획만 제거·모임/초대 유지·15개 자리 복귀</t>
+          <t>사용자 순서 유지·비운 제목은 날짜</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI12</t>
+          <t>UI12</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -4206,24 +4206,24 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>TC-F11-02</t>
+          <t>TC-F10-02</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>빈 방문·빈 일정 삭제 (P05)</t>
+          <t>방문 계획 편집</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -4233,17 +4233,17 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>숨김/보존파일·진행업로드 있는 일정 삭제</t>
+          <t>방문 누락·중복·다른 날짜 혼입</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>거부·취소로 안내</t>
+          <t>전체 저장 거부</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI12</t>
+          <t>UI12</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -4268,17 +4268,17 @@
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TC-F11-03</t>
+          <t>TC-F10-03</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>빈 방문·빈 일정 삭제 (P05)</t>
+          <t>방문 계획 편집</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4288,17 +4288,17 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>업로드접수와삭제 순서 양방향 경쟁</t>
+          <t>시각23:55/24:00·제목30/31자·시각순 정렬 버튼</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>먼저 확정한 상태 기준·늦은 접수/삭제 거부</t>
+          <t>23:55/30자만 허용·버튼 눌렀을 때만 재정렬</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI12</t>
+          <t>UI12</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -4316,24 +4316,24 @@
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>TC-F11-04</t>
+          <t>TC-F10-04</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F10</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>빈 방문·빈 일정 삭제 (P05)</t>
+          <t>방문 계획 편집</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -4343,17 +4343,17 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>삭제 재시도·삭제된 일정 상세 진입</t>
+          <t>동시계획 수정·미저장 이탈</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>멱등 결과·재생성 없음·삭제 안내</t>
+          <t>먼저 저장 유지·입력 보존·저장/버리기/계속</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>UI05, UI06, UI12</t>
+          <t>UI12</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -4371,24 +4371,24 @@
       <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>TC-F12-01</t>
+          <t>TC-F11-01</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>사진·짧은 영상 촬영</t>
+          <t>빈 방문·빈 일정 삭제 (P05)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1~5초 자동종료·3초최초·다음실행값</t>
+          <t>빈방문·마지막빈일정 삭제</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>선택값±0.25초·기기 마지막값 기억</t>
+          <t>관련 빈 계획만 제거·모임/초대 유지·15개 자리 복귀</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>UI14, UI15</t>
+          <t>UI05, UI06, UI12</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4426,24 +4426,24 @@
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>TC-F12-02</t>
+          <t>TC-F11-02</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>사진·짧은 영상 촬영</t>
+          <t>빈 방문·빈 일정 삭제 (P05)</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>녹화 조기종료0.49/0.50초</t>
+          <t>숨김/보존파일·진행업로드 있는 일정 삭제</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>0.49거부·0.50초 유효파일 허용</t>
+          <t>거부·취소로 안내</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>UI14, UI15</t>
+          <t>UI05, UI06, UI12</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -4481,24 +4481,24 @@
       <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>TC-F12-03</t>
+          <t>TC-F11-03</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>사진·짧은 영상 촬영</t>
+          <t>빈 방문·빈 일정 삭제 (P05)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>마이크거절·카메라거절·녹화중전후면</t>
+          <t>업로드접수와삭제 순서 양방향 경쟁</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>무음허용·카메라거절안내·녹화중전환불가</t>
+          <t>먼저 확정한 상태 기준·늦은 접수/삭제 거부</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>UI14, UI15</t>
+          <t>UI05, UI06, UI12</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4536,24 +4536,24 @@
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>TC-F12-04</t>
+          <t>TC-F11-04</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F12</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>사진·짧은 영상 촬영</t>
+          <t>빈 방문·빈 일정 삭제 (P05)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>앱전환·전화·공간부족·취소</t>
+          <t>삭제 재시도·삭제된 일정 상세 진입</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>유효결과만 후보·기존업로드/기기원본 유지</t>
+          <t>멱등 결과·재생성 없음·삭제 안내</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>UI14, UI15</t>
+          <t>UI05, UI06, UI12</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -4591,24 +4591,24 @@
       <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>TC-F13-01</t>
+          <t>TC-F12-01</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>기기 사진·영상 가져오기</t>
+          <t>사진·짧은 영상 촬영</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>사진/영상/촬영 혼합120개·여러번선택</t>
+          <t>1~5초 자동종료·3초최초·다음실행값</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>최초선택순서 유지·후보 합산120개</t>
+          <t>선택값±0.25초·기기 마지막값 기억</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>UI14, UI16</t>
+          <t>UI14, UI15</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>TC-F13-02</t>
+          <t>TC-F12-02</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>기기 사진·영상 가져오기</t>
+          <t>사진·짧은 영상 촬영</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4673,17 +4673,17 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>0/120/121개·영상60/60.1초·200MB+1바이트</t>
+          <t>녹화 조기종료0.49/0.50초</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>상한 초과만 거부·자동자르기 없음</t>
+          <t>0.49거부·0.50초 유효파일 허용</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>UI14, UI16</t>
+          <t>UI14, UI15</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
@@ -4708,17 +4708,17 @@
     <row r="52" ht="34" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TC-F13-03</t>
+          <t>TC-F12-03</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>기기 사진·영상 가져오기</t>
+          <t>사진·짧은 영상 촬영</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -4728,17 +4728,17 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>손상·RAW·애니메이션·접근소실 혼합</t>
+          <t>마이크거절·카메라거절·녹화중전후면</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>파일별 오류·나머지 후보 유지</t>
+          <t>무음허용·카메라거절안내·녹화중전환불가</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>UI14, UI16</t>
+          <t>UI14, UI15</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4763,17 +4763,17 @@
     <row r="53" ht="34" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>TC-F13-04</t>
+          <t>TC-F12-04</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F12</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>기기 사진·영상 가져오기</t>
+          <t>사진·짧은 영상 촬영</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4783,17 +4783,17 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>방문 남은 개수 사진3/5·영상0/2 표시 후 초과 선택</t>
+          <t>앱전환·전화·공간부족·취소</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>남은 개수 표시·초과분은 확인 단계에서 파일별 표시</t>
+          <t>유효결과만 후보·기존업로드/기기원본 유지</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>UI14, UI16</t>
+          <t>UI14, UI15</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -4818,17 +4818,17 @@
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>TC-F14-01</t>
+          <t>TC-F13-01</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
+          <t>기기 사진·영상 가져오기</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>단일일/오늘포함다일/범위밖오늘·방문진입</t>
+          <t>사진/영상/촬영 혼합120개·여러번선택</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>기본 기록일 제안 규칙 일치</t>
+          <t>최초선택순서 유지·후보 합산120개</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>UI13, UI14, UI16</t>
+          <t>UI14, UI16</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4866,24 +4866,24 @@
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>TC-F14-02</t>
+          <t>TC-F13-02</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
+          <t>기기 사진·영상 가져오기</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>같은 방문에 사진6·영상3 제출·미지정 묶음 한도</t>
+          <t>0/120/121개·영상60/60.1초·200MB+1바이트</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>사진5·영상2만 접수·초과 파일별 MEDIA_LIMIT·작성자×일정×기록일 적용</t>
+          <t>상한 초과만 거부·자동자르기 없음</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>UI13, UI14, UI16</t>
+          <t>UI14, UI16</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -4921,24 +4921,24 @@
       <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="56" ht="34" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>TC-F14-03</t>
+          <t>TC-F13-03</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
+          <t>기기 사진·영상 가져오기</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -4948,17 +4948,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>두 기기 동시 접수·실패/취소 자리 즉시 반환·삭제 후 반환</t>
+          <t>손상·RAW·애니메이션·접근소실 혼합</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>합산 한도 유지·반환 시점 일치·중복 반환 없음</t>
+          <t>파일별 오류·나머지 후보 유지</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>UI13, UI14, UI16</t>
+          <t>UI14, UI16</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4976,24 +4976,24 @@
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="57" ht="34" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>TC-F14-04</t>
+          <t>TC-F13-04</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F14</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
+          <t>기기 사진·영상 가져오기</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>설명1000/1001자·취소일정·기한경과·방문일불일치</t>
+          <t>방문 남은 개수 사진3/5·영상0/2 표시 후 초과 선택</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>초과/신규접수 거부·설명 일반텍스트·불일치 거부</t>
+          <t>남은 개수 표시·초과분은 확인 단계에서 파일별 표시</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>UI13, UI14, UI16</t>
+          <t>UI14, UI16</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -5031,44 +5031,44 @@
       <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="58" ht="34" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>TC-F15-01</t>
+          <t>TC-F14-01</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>F15</t>
+          <t>F14</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>파일 전송·재시도·취소</t>
+          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>일부완료·일부실패·100%서버검사중</t>
+          <t>단일일/오늘포함다일/범위밖오늘·방문진입</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>완료만공개·실패만재시도·100%≠완료</t>
+          <t>기본 기록일 제안 규칙 일치</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI35</t>
+          <t>UI13, UI14, UI16</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -5093,37 +5093,37 @@
     <row r="59" ht="34" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>TC-F15-02</t>
+          <t>TC-F14-02</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F15</t>
+          <t>F14</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>파일 전송·재시도·취소</t>
+          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>전송실패 자동재시도·오프라인대기</t>
+          <t>같은 방문에 사진6·영상3 제출·미지정 묶음 한도</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>1/2/4초3회·오프라인횟수미소모·동시3개</t>
+          <t>사진5·영상2만 접수·초과 파일별 MEDIA_LIMIT·작성자×일정×기록일 적용</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI35</t>
+          <t>UI13, UI14, UI16</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -5148,37 +5148,37 @@
     <row r="60" ht="34" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>TC-F15-03</t>
+          <t>TC-F14-03</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>F15</t>
+          <t>F14</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>파일 전송·재시도·취소</t>
+          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>프로세스종료/강제종료 후 재실행</t>
+          <t>두 기기 동시 접수·실패/취소 자리 즉시 반환·삭제 후 반환</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>서버확인 후 복구·새계정제출 없음</t>
+          <t>합산 한도 유지·반환 시점 일치·중복 반환 없음</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI35</t>
+          <t>UI13, UI14, UI16</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -5196,44 +5196,44 @@
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="61" ht="34" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>TC-F15-04</t>
+          <t>TC-F14-04</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F15</t>
+          <t>F14</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>파일 전송·재시도·취소</t>
+          <t>업로드 확인·파일별 정보 입력 (P10·P11)</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>완료/취소·취소일정기존작업/퇴장/모임종료 경쟁</t>
+          <t>설명1000/1001자·취소일정·기한경과·방문일불일치</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>서버최종상태 일치·권한/종료/만료 우선</t>
+          <t>초과/신규접수 거부·설명 일반텍스트·불일치 거부</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI35</t>
+          <t>UI13, UI14, UI16</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
@@ -5251,44 +5251,44 @@
       <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="62" ht="34" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>TC-F16-01</t>
+          <t>TC-F15-01</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F15</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>공동 기록 목록·사진 감상·영상 재생</t>
+          <t>파일 전송·재시도·취소</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>시간순 오름/내림·촬영시각 없는 파일</t>
+          <t>일부완료·일부실패·100%서버검사중</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>촬영시각 기준·없는 파일은 완료시각 사용+표시·동일시각 ID 고정</t>
+          <t>완료만공개·실패만재시도·100%≠완료</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>UI08, UI09, UI13, UI18</t>
+          <t>UI17, UI35</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5313,37 +5313,37 @@
     <row r="63" ht="34" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>TC-F16-02</t>
+          <t>TC-F15-02</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F15</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>공동 기록 목록·사진 감상·영상 재생</t>
+          <t>파일 전송·재시도·취소</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>사람별 묶음·작성자 구역 순서·접기·60개 페이지 경계</t>
+          <t>전송실패 자동재시도·오프라인대기</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>먼저 완료 작성자부터·구역 내부 시간순·중복없는 커서·집합 동일</t>
+          <t>1/2/4초3회·오프라인횟수미소모·동시3개</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>UI08, UI09, UI13, UI18</t>
+          <t>UI17, UI35</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -5368,37 +5368,37 @@
     <row r="64" ht="34" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>TC-F16-03</t>
+          <t>TC-F15-03</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F15</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>공동 기록 목록·사진 감상·영상 재생</t>
+          <t>파일 전송·재시도·취소</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>차단·운영제한·삭제·만료 혼합·장소/작성자별 집계</t>
+          <t>프로세스종료/강제종료 후 재실행</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>목록과 집계 일치·차단 작성자 구역 없음</t>
+          <t>서버확인 후 복구·새계정제출 없음</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>UI08, UI09, UI13, UI18</t>
+          <t>UI17, UI35</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5423,37 +5423,37 @@
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>TC-F16-04</t>
+          <t>TC-F15-04</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F15</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>공동 기록 목록·사진 감상·영상 재생</t>
+          <t>파일 전송·재시도·취소</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>길게 눌러 선택 모드·영상종료/확대닫기·업로더기기꺼짐</t>
+          <t>완료/취소·취소일정기존작업/퇴장/모임종료 경쟁</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>UI16 선택 진입·소리중단·보기방식/스크롤 복원·서버열람 가능</t>
+          <t>서버최종상태 일치·권한/종료/만료 우선</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>UI08, UI09, UI13, UI18</t>
+          <t>UI17, UI35</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -5471,44 +5471,44 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="66" ht="34" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>TC-F17-01</t>
+          <t>TC-F16-01</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>F17</t>
+          <t>F16</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>본인 기록 개별·일괄 정보 수정</t>
+          <t>공동 기록 목록·사진 감상·영상 재생</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>필드별 적용/유지·설명비우기·방문해제</t>
+          <t>시간순 오름/내림·촬영시각 없는 파일</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>선택한 필드만 전체 대상 반영</t>
+          <t>촬영시각 기준·없는 파일은 완료시각 사용+표시·동일시각 ID 고정</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI20</t>
+          <t>UI08, UI09, UI13, UI18</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5533,37 +5533,37 @@
     <row r="67" ht="34" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>TC-F17-02</t>
+          <t>TC-F16-02</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F17</t>
+          <t>F16</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>본인 기록 개별·일괄 정보 수정</t>
+          <t>공동 기록 목록·사진 감상·영상 재생</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>다른일정/타인/121개·기간밖기록 재지정</t>
+          <t>사람별 묶음·작성자 구역 순서·접기·60개 페이지 경계</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>혼합요청거부·기간안 재지정허용</t>
+          <t>먼저 완료 작성자부터·구역 내부 시간순·중복없는 커서·집합 동일</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI20</t>
+          <t>UI08, UI09, UI13, UI18</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -5588,37 +5588,37 @@
     <row r="68" ht="34" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TC-F17-03</t>
+          <t>TC-F16-03</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>F17</t>
+          <t>F16</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>본인 기록 개별·일괄 정보 수정</t>
+          <t>공동 기록 목록·사진 감상·영상 재생</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>방문 변경으로 대상 방문 사진5 초과·검사중 버전 변경</t>
+          <t>차단·운영제한·삭제·만료 혼합·장소/작성자별 집계</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>해당 파일 MEDIA_LIMIT·전체 미적용·입력 유지</t>
+          <t>목록과 집계 일치·차단 작성자 구역 없음</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI20</t>
+          <t>UI08, UI09, UI13, UI18</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5643,37 +5643,37 @@
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>TC-F17-04</t>
+          <t>TC-F16-04</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>F17</t>
+          <t>F16</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>본인 기록 개별·일괄 정보 수정</t>
+          <t>공동 기록 목록·사진 감상·영상 재생</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>설명검사거부·응답유실 재시도</t>
+          <t>길게 눌러 선택 모드·영상종료/확대닫기·업로더기기꺼짐</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>전체미적용 또는 동일요청결과·집계중복없음</t>
+          <t>UI16 선택 진입·소리중단·보기방식/스크롤 복원·서버열람 가능</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI20</t>
+          <t>UI08, UI09, UI13, UI18</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -5698,17 +5698,17 @@
     <row r="70" ht="34" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TC-F18-01</t>
+          <t>TC-F17-01</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
+          <t>본인 기록 개별·일괄 정보 수정</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -5718,17 +5718,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>나간/퇴장/종료 모임 본인파일 열람·삭제</t>
+          <t>필드별 적용/유지·설명비우기·방문해제</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>참여/빈자리 불필요·타인공동자료 비노출</t>
+          <t>선택한 필드만 전체 대상 반영</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI09, UI16, UI18, UI20</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5753,17 +5753,17 @@
     <row r="71" ht="34" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>TC-F18-02</t>
+          <t>TC-F17-02</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
+          <t>본인 기록 개별·일괄 정보 수정</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -5773,17 +5773,17 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>여러모임 본인120개 삭제·타인1개혼합</t>
+          <t>다른일정/타인/121개·기간밖기록 재지정</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>본인혼합허용·권한오류는 요청전체거부</t>
+          <t>혼합요청거부·기간안 재지정허용</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI09, UI16, UI18, UI20</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
@@ -5808,17 +5808,17 @@
     <row r="72" ht="34" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TC-F18-03</t>
+          <t>TC-F17-03</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
+          <t>본인 기록 개별·일괄 정보 수정</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -5828,17 +5828,17 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>유효요청 중 일부정리실패·이미삭제 재요청</t>
+          <t>방문 변경으로 대상 방문 사진5 초과·검사중 버전 변경</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>파일별결과·실패만재시도·중복차감없음</t>
+          <t>해당 파일 MEDIA_LIMIT·전체 미적용·입력 유지</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI09, UI16, UI18, UI20</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5863,17 +5863,17 @@
     <row r="73" ht="34" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>TC-F18-04</t>
+          <t>TC-F17-04</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>F18</t>
+          <t>F17</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
+          <t>본인 기록 개별·일괄 정보 수정</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -5883,17 +5883,17 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>참여종료 본인 저장/정보수정 직접요청</t>
+          <t>설명검사거부·응답유실 재시도</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>거부·열람/삭제만 허용</t>
+          <t>전체미적용 또는 동일요청결과·집계중복없음</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI09, UI16, UI18, UI20</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
@@ -5918,37 +5918,37 @@
     <row r="74" ht="34" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>TC-F19-01</t>
+          <t>TC-F18-01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>F19</t>
+          <t>F18</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>사진·영상 휴대폰 저장</t>
+          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>길게 눌러 본인/타인120개 선택 저장</t>
+          <t>나간/퇴장/종료 모임 본인파일 열람·삭제</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>참여자 동일권한·UI16 공통 선택 화면·앨범 경로 표시</t>
+          <t>참여/빈자리 불필요·타인공동자료 비노출</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI21</t>
+          <t>UI16, UI18, UI22, UI28</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5966,44 +5966,44 @@
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="75" ht="34" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>TC-F19-02</t>
+          <t>TC-F18-02</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F19</t>
+          <t>F18</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>사진·영상 휴대폰 저장</t>
+          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>기기공간부족·부분다운로드실패</t>
+          <t>여러모임 본인120개 삭제·타인1개혼합</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>실패개수·재시도/선택축소</t>
+          <t>본인혼합허용·권한오류는 요청전체거부</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI21</t>
+          <t>UI16, UI18, UI22, UI28</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -6021,44 +6021,44 @@
       <c r="L75" s="3" t="inlineStr"/>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="76" ht="34" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>TC-F19-03</t>
+          <t>TC-F18-03</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>F19</t>
+          <t>F18</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>사진·영상 휴대폰 저장</t>
+          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>내려받기100%·기기쓰기 전 이탈</t>
+          <t>유효요청 중 일부정리실패·이미삭제 재요청</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>쓰기 전 완료로 표시하지 않음</t>
+          <t>파일별결과·실패만재시도·중복차감없음</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI21</t>
+          <t>UI16, UI18, UI22, UI28</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6076,44 +6076,44 @@
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="77" ht="34" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>TC-F19-04</t>
+          <t>TC-F18-04</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F19</t>
+          <t>F18</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>사진·영상 휴대폰 저장</t>
+          <t>내가 올린 기록 조회·개별/일괄 삭제</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>파일준비 뒤 퇴장·만료·개인차단·purpose=share 요청</t>
+          <t>참여종료 본인 저장/정보수정 직접요청</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>파일스트림 재검증으로 거부·share는 400 거부</t>
+          <t>거부·열람/삭제만 허용</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>UI09, UI16, UI18, UI21</t>
+          <t>UI16, UI18, UI22, UI28</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -6131,44 +6131,44 @@
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="78" ht="34" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TC-F20-01</t>
+          <t>TC-F19-01</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>F19</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>촬영 위치 메타데이터 처리 (P07)</t>
+          <t>사진·영상 휴대폰 저장</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>GPS있는/없는 사진·영상·대표사진 타인제공</t>
+          <t>길게 눌러 본인/타인120개 선택 저장</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>썸네일/열람/저장 모두위치태그없음</t>
+          <t>참여자 동일권한·UI16 공통 선택 화면·앨범 경로 표시</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI21</t>
+          <t>UI09, UI16, UI18, UI21</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6186,44 +6186,44 @@
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>실파일 fixture + 메타데이터/호환성 검사</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>TC-F20-02</t>
+          <t>TC-F19-02</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>F19</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>촬영 위치 메타데이터 처리 (P07)</t>
+          <t>사진·영상 휴대폰 저장</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>회전·촬영시각·음성·HDR 입력</t>
+          <t>기기공간부족·부분다운로드실패</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>정보보존·호환본SDR·전체구간 유지</t>
+          <t>실패개수·재시도/선택축소</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI21</t>
+          <t>UI09, UI16, UI18, UI21</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
@@ -6241,44 +6241,44 @@
       <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>실파일 fixture + 메타데이터/호환성 검사</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="80" ht="34" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TC-F20-03</t>
+          <t>TC-F19-03</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>F19</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>촬영 위치 메타데이터 처리 (P07)</t>
+          <t>사진·영상 휴대폰 저장</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>제거검증실패·알수없는메타데이터</t>
+          <t>내려받기100%·기기쓰기 전 이탈</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>공개/준비완료 금지·재시도/안내</t>
+          <t>쓰기 전 완료로 표시하지 않음</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI21</t>
+          <t>UI09, UI16, UI18, UI21</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6296,44 +6296,44 @@
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>실파일 fixture + 메타데이터/호환성 검사</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>TC-F20-04</t>
+          <t>TC-F19-04</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>F20</t>
+          <t>F19</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>촬영 위치 메타데이터 처리 (P07)</t>
+          <t>사진·영상 휴대폰 저장</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>기기원본과 앱별도방문 위치 비교</t>
+          <t>파일준비 뒤 퇴장·만료·개인차단·purpose=share 요청</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>기기원본불변·사용자지정방문 유지</t>
+          <t>파일스트림 재검증으로 거부·share는 400 거부</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI21</t>
+          <t>UI09, UI16, UI18, UI21</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -6351,24 +6351,24 @@
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>실파일 fixture + 메타데이터/호환성 검사</t>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TC-F21-01</t>
+          <t>TC-F20-01</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>일정별 보관·만료 (P01)</t>
+          <t>촬영 위치 메타데이터 처리 (P07)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6378,17 +6378,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2027.01.31종료 첫완료</t>
+          <t>GPS있는/없는 사진·영상·대표사진 타인제공</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>04.30까지·05.01 00:00 KST 만료</t>
+          <t>썸네일/열람/저장 모두위치태그없음</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI08, UI22</t>
+          <t>UI17, UI21</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6406,24 +6406,24 @@
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>실파일 fixture + 메타데이터/호환성 검사</t>
         </is>
       </c>
     </row>
     <row r="83" ht="34" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>TC-F21-02</t>
+          <t>TC-F20-02</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>일정별 보관·만료 (P01)</t>
+          <t>촬영 위치 메타데이터 처리 (P07)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -6433,17 +6433,17 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>첫완료와종료일변경 동시·모든파일삭제후재업로드</t>
+          <t>회전·촬영시각·음성·HDR 입력</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>서버확정기준 단일기한·고정해제없음</t>
+          <t>정보보존·호환본SDR·전체구간 유지</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI08, UI22</t>
+          <t>UI17, UI21</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
@@ -6461,24 +6461,24 @@
       <c r="L83" s="3" t="inlineStr"/>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>실파일 fixture + 메타데이터/호환성 검사</t>
         </is>
       </c>
     </row>
     <row r="84" ht="34" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>TC-F21-03</t>
+          <t>TC-F20-03</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>일정별 보관·만료 (P01)</t>
+          <t>촬영 위치 메타데이터 처리 (P07)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>취소전접수 첫파일 취소후완료·예상기한경과</t>
+          <t>제거검증실패·알수없는메타데이터</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>취소직전종료일 기준·지난기한완료거부</t>
+          <t>공개/준비완료 금지·재시도/안내</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI08, UI22</t>
+          <t>UI17, UI21</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6516,24 +6516,24 @@
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>실파일 fixture + 메타데이터/호환성 검사</t>
         </is>
       </c>
     </row>
     <row r="85" ht="34" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>TC-F21-04</t>
+          <t>TC-F20-04</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>F21</t>
+          <t>F20</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>일정별 보관·만료 (P01)</t>
+          <t>촬영 위치 메타데이터 처리 (P07)</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6543,17 +6543,17 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>만료경계·7일/1일전·만료후30일카드</t>
+          <t>기기원본과 앱별도방문 위치 비교</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>즉시접근차단·앱내안내·카드는설명없이기한만</t>
+          <t>기기원본불변·사용자지정방문 유지</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI08, UI22</t>
+          <t>UI17, UI21</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -6571,24 +6571,24 @@
       <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>고정 시계 도메인 단위 + API 통합</t>
+          <t>실파일 fixture + 메타데이터/호환성 검사</t>
         </is>
       </c>
     </row>
     <row r="86" ht="34" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>TC-F22-01</t>
+          <t>TC-F21-01</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
+          <t>일정별 보관·만료 (P01)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -6598,17 +6598,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>방장이활성참여자에게이전</t>
+          <t>2027.01.31종료 첫완료</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>즉시이전·수락대기없음·방장한명</t>
+          <t>04.30까지·05.01 00:00 KST 만료</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>UI26, UI27</t>
+          <t>UI03, UI08, UI22</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6626,24 +6626,24 @@
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="87" ht="34" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>TC-F22-02</t>
+          <t>TC-F21-02</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
+          <t>일정별 보관·만료 (P01)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6653,17 +6653,17 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>본인지정·탈퇴대상·일반참여자이전요청</t>
+          <t>첫완료와종료일변경 동시·모든파일삭제후재업로드</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>거부·기존방장유지</t>
+          <t>서버확정기준 단일기한·고정해제없음</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>UI26, UI27</t>
+          <t>UI03, UI08, UI22</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -6681,24 +6681,24 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="88" ht="34" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TC-F22-03</t>
+          <t>TC-F21-03</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
+          <t>일정별 보관·만료 (P01)</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -6708,17 +6708,17 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>퇴장→차단해제→새참여→오래된퇴장재시도</t>
+          <t>취소전접수 첫파일 취소후완료·예상기한경과</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>새membershipId보존·차단재생성없음</t>
+          <t>취소직전종료일 기준·지난기한완료거부</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>UI26, UI27</t>
+          <t>UI03, UI08, UI22</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -6736,24 +6736,24 @@
       <c r="L88" s="2" t="inlineStr"/>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="89" ht="34" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>TC-F22-04</t>
+          <t>TC-F21-04</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>F22</t>
+          <t>F21</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
+          <t>일정별 보관·만료 (P01)</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6763,17 +6763,17 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>강제퇴장과자발나가기 비교</t>
+          <t>만료경계·7일/1일전·만료후30일카드</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>강제만재참여차단·완료파일기한/소유유지</t>
+          <t>즉시접근차단·앱내안내·카드는설명없이기한만</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>UI26, UI27</t>
+          <t>UI03, UI08, UI22</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
@@ -6791,24 +6791,24 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>고정 시계 도메인 단위 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="90" ht="34" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TC-F23-01</t>
+          <t>TC-F22-01</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>F23</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>나가기·마지막 방장 모임 종료 (P02)</t>
+          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6818,17 +6818,17 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>일반나가기 후 본인조회/삭제</t>
+          <t>방장이활성참여자에게이전</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>공동접근종료·유효파일유지·새저장불가</t>
+          <t>즉시이전·수락대기없음·방장한명</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>UI27</t>
+          <t>UI26, UI27</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -6853,17 +6853,17 @@
     <row r="91" ht="34" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>TC-F23-02</t>
+          <t>TC-F22-02</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>F23</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>나가기·마지막 방장 모임 종료 (P02)</t>
+          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6873,17 +6873,17 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>2인이상방장나가기/전체종료</t>
+          <t>본인지정·탈퇴대상·일반참여자이전요청</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>이전전나가기/전체종료 거부</t>
+          <t>거부·기존방장유지</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>UI27</t>
+          <t>UI26, UI27</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -6908,17 +6908,17 @@
     <row r="92" ht="34" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TC-F23-03</t>
+          <t>TC-F22-03</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>F23</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>나가기·마지막 방장 모임 종료 (P02)</t>
+          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>마지막방장종료·과거타인파일포함</t>
+          <t>퇴장→차단해제→새참여→오래된퇴장재시도</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>본인만삭제·타인본인경로보존·재개불가</t>
+          <t>새membershipId보존·차단재생성없음</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>UI27</t>
+          <t>UI26, UI27</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -6963,17 +6963,17 @@
     <row r="93" ht="34" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>TC-F23-04</t>
+          <t>TC-F22-04</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>F23</t>
+          <t>F22</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>나가기·마지막 방장 모임 종료 (P02)</t>
+          <t>참여자 목록·방장 이전·강제 퇴장 (P03)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>동시새참여와종료 양방향 순서</t>
+          <t>강제퇴장과자발나가기 비교</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>새참여먼저면종료거부·종료먼저면참여거부</t>
+          <t>강제만재참여차단·완료파일기한/소유유지</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>UI27</t>
+          <t>UI26, UI27</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
@@ -7011,24 +7011,24 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="94" ht="34" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TC-F24-01</t>
+          <t>TC-F23-01</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>F24</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>계정 삭제</t>
+          <t>나가기·마지막 방장 모임 종료 (P02)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7038,17 +7038,17 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>방장역할미정리·역할정리완료</t>
+          <t>일반나가기 후 본인조회/삭제</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>미정리거부·정리후전체본인파일삭제</t>
+          <t>공동접근종료·유효파일유지·새저장불가</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>UI28, UI30</t>
+          <t>UI27</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7073,17 +7073,17 @@
     <row r="95" ht="34" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>TC-F24-02</t>
+          <t>TC-F23-02</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>F24</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>계정 삭제</t>
+          <t>나가기·마지막 방장 모임 종료 (P02)</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -7093,17 +7093,17 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>나간/퇴장/종료모임의본인파일 포함</t>
+          <t>2인이상방장나가기/전체종료</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>작성자ID전체탐색·타인파일유지</t>
+          <t>이전전나가기/전체종료 거부</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>UI28, UI30</t>
+          <t>UI27</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
@@ -7128,17 +7128,17 @@
     <row r="96" ht="34" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>TC-F24-03</t>
+          <t>TC-F23-03</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>F24</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>계정 삭제</t>
+          <t>나가기·마지막 방장 모임 종료 (P02)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -7148,17 +7148,17 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>삭제직전모임생성/방장수신 경쟁</t>
+          <t>마지막방장종료·과거타인파일포함</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>계정잠금으로선행조건재검증</t>
+          <t>본인만삭제·타인본인경로보존·재개불가</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>UI28, UI30</t>
+          <t>UI27</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7176,24 +7176,24 @@
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="97" ht="34" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>TC-F24-04</t>
+          <t>TC-F23-04</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>F24</t>
+          <t>F23</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>계정 삭제</t>
+          <t>나가기·마지막 방장 모임 종료 (P02)</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -7203,17 +7203,17 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>삭제재시도·재가입·정리실패</t>
+          <t>동시새참여와종료 양방향 순서</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>즉시접근차단·중복집계없음·기록자동복구없음</t>
+          <t>새참여먼저면종료거부·종료먼저면참여거부</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>UI28, UI30</t>
+          <t>UI27</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
@@ -7231,44 +7231,44 @@
       <c r="L97" s="3" t="inlineStr"/>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>API 통합 + Android 화면 확인</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="98" ht="34" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>TC-F25-01</t>
+          <t>TC-F24-01</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>F25</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>신고·개인 차단 (P08)</t>
+          <t>계정 삭제</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>파일/대표사진/참여자신고·중복요청</t>
+          <t>방장역할미정리·역할정리완료</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>최소증거연결·중복없음·자동삭제없음</t>
+          <t>미정리거부·정리후전체본인파일삭제</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>UI18, UI26, UI31, UI34</t>
+          <t>UI28, UI30</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7286,44 +7286,44 @@
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>API 권한 + 운영 시나리오 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="99" ht="34" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>TC-F25-02</t>
+          <t>TC-F24-02</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>F25</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>신고·개인 차단 (P08)</t>
+          <t>계정 삭제</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>개인차단 뒤공동목록/집계/직접저장공유</t>
+          <t>나간/퇴장/종료모임의본인파일 포함</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>내경로만숨김·집계일치</t>
+          <t>작성자ID전체탐색·타인파일유지</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>UI18, UI26, UI31, UI34</t>
+          <t>UI28, UI30</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -7341,44 +7341,44 @@
       <c r="L99" s="3" t="inlineStr"/>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>API 권한 + 운영 시나리오 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="100" ht="34" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>TC-F25-03</t>
+          <t>TC-F24-03</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>F25</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>신고·개인 차단 (P08)</t>
+          <t>계정 삭제</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>방장개인차단·모임재참여차단비교</t>
+          <t>삭제직전모임생성/방장수신 경쟁</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>방장역할유지·두차단독립</t>
+          <t>계정잠금으로선행조건재검증</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>UI18, UI26, UI31, UI34</t>
+          <t>UI28, UI30</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7396,44 +7396,44 @@
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>API 권한 + 운영 시나리오 수동</t>
+          <t>DB 경쟁 + API 통합</t>
         </is>
       </c>
     </row>
     <row r="101" ht="34" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>TC-F25-04</t>
+          <t>TC-F24-04</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>F25</t>
+          <t>F24</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>신고·개인 차단 (P08)</t>
+          <t>계정 삭제</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>신고결과/이의·타인신고자정보요청</t>
+          <t>삭제재시도·재가입·정리실패</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>본인결과조회·타인신원/증거비공개</t>
+          <t>즉시접근차단·중복집계없음·기록자동복구없음</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>UI18, UI26, UI31, UI34</t>
+          <t>UI28, UI30</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -7451,44 +7451,44 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>API 권한 + 운영 시나리오 수동</t>
+          <t>API 통합 + Android 화면 확인</t>
         </is>
       </c>
     </row>
     <row r="102" ht="34" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TC-F26-01</t>
+          <t>TC-F25-01</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
+          <t>신고·개인 차단 (P08)</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>사진/영상/이름/제목/주소/설명 공개전검사</t>
+          <t>파일/대표사진/참여자신고·중복요청</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>통과전비공개·수정은기존공개값유지</t>
+          <t>최소증거연결·중복없음·자동삭제없음</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI31, UI34</t>
+          <t>UI18, UI26, UI31, UI34</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7513,37 +7513,37 @@
     <row r="103" ht="34" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>TC-F26-02</t>
+          <t>TC-F25-02</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
+          <t>신고·개인 차단 (P08)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>엔진장애·판정불가·의심콘텐츠</t>
+          <t>개인차단 뒤공동목록/집계/직접저장공유</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>비공개수동검토·자동공개없음</t>
+          <t>내경로만숨김·집계일치</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI31, UI34</t>
+          <t>UI18, UI26, UI31, UI34</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -7568,37 +7568,37 @@
     <row r="104" ht="34" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>TC-F26-03</t>
+          <t>TC-F25-03</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
+          <t>신고·개인 차단 (P08)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>운영자제한/삭제/해제·일반방장같은요청</t>
+          <t>방장개인차단·모임재참여차단비교</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>운영권한/감사이력·방장거부</t>
+          <t>방장역할유지·두차단독립</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>UI17, UI31, UI34</t>
+          <t>UI18, UI26, UI31, UI34</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -7623,37 +7623,37 @@
     <row r="105" ht="34" customHeight="1">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>TC-F26-04</t>
+          <t>TC-F25-04</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>F26</t>
+          <t>F25</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
+          <t>신고·개인 차단 (P08)</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>서비스제한계정·종료모임보존파일 조치</t>
+          <t>신고결과/이의·타인신고자정보요청</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>열람등정책적용·본인삭제/동의철회/문의유지</t>
+          <t>본인결과조회·타인신원/증거비공개</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>UI17, UI31, UI34</t>
+          <t>UI18, UI26, UI31, UI34</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
@@ -7678,37 +7678,37 @@
     <row r="106" ht="34" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>TC-F27-01</t>
+          <t>TC-F26-01</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>방장 부재 수동 복구 (P04)</t>
+          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>요청자재인증·후임별도동의·기존방장통지</t>
+          <t>사진/영상/이름/제목/주소/설명 공개전검사</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>자료/통지이력·7일응답대기</t>
+          <t>통과전비공개·수정은기존공개값유지</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>UI32, UI34</t>
+          <t>UI17, UI31, UI34</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -7733,37 +7733,37 @@
     <row r="107" ht="34" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>TC-F27-02</t>
+          <t>TC-F26-02</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>방장 부재 수동 복구 (P04)</t>
+          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>7일경과·이견/증거부족</t>
+          <t>엔진장애·판정불가·의심콘텐츠</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>자동승인없음·수동검토/보류</t>
+          <t>비공개수동검토·자동공개없음</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>UI32, UI34</t>
+          <t>UI17, UI31, UI34</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
@@ -7788,37 +7788,37 @@
     <row r="108" ht="34" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>TC-F27-03</t>
+          <t>TC-F26-03</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>방장 부재 수동 복구 (P04)</t>
+          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>승인직전직접이전/후임나감/모임종료</t>
+          <t>운영자제한/삭제/해제·일반방장같은요청</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>버전검증거부·오래된승인미덮어씀</t>
+          <t>운영권한/감사이력·방장거부</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>UI32, UI34</t>
+          <t>UI17, UI31, UI34</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -7843,37 +7843,37 @@
     <row r="109" ht="34" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>TC-F27-04</t>
+          <t>TC-F26-04</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>F27</t>
+          <t>F26</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>방장 부재 수동 복구 (P04)</t>
+          <t>유해 콘텐츠 검사·운영 조치 (P08)</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>복구승인과파일기한/작성자 비교</t>
+          <t>서비스제한계정·종료모임보존파일 조치</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>방장역할만변경·기한/소유불변·종료재개불가</t>
+          <t>열람등정책적용·본인삭제/동의철회/문의유지</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>UI32, UI34</t>
+          <t>UI17, UI31, UI34</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
@@ -7898,17 +7898,17 @@
     <row r="110" ht="34" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>TC-F28-01</t>
+          <t>TC-F27-01</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>F28</t>
+          <t>F27</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>저장 공간·캐시·로그아웃·문의</t>
+          <t>방장 부재 수동 복구 (P04)</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -7918,17 +7918,17 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>완료원본+예약=5GB경계·동시접수</t>
+          <t>요청자재인증·후임별도동의·기존방장통지</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>동시초과없음·파생본사용량별도</t>
+          <t>자료/통지이력·7일응답대기</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI32, UI34</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -7946,24 +7946,24 @@
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>DB 경쟁 + API 통합</t>
+          <t>API 권한 + 운영 시나리오 수동</t>
         </is>
       </c>
     </row>
     <row r="111" ht="34" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>TC-F28-02</t>
+          <t>TC-F27-02</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>F28</t>
+          <t>F27</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>저장 공간·캐시·로그아웃·문의</t>
+          <t>방장 부재 수동 복구 (P04)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>캐시500MB LRU정리·미완료원본포함</t>
+          <t>7일경과·이견/증거부족</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>재생캐시만삭제·유일원본/설명/작업유지</t>
+          <t>자동승인없음·수동검토/보류</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI32, UI34</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
@@ -8001,24 +8001,24 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 권한 + 운영 시나리오 수동</t>
         </is>
       </c>
     </row>
     <row r="112" ht="34" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>TC-F28-03</t>
+          <t>TC-F27-03</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>F28</t>
+          <t>F27</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>저장 공간·캐시·로그아웃·문의</t>
+          <t>방장 부재 수동 복구 (P04)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -8028,17 +8028,17 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>로그아웃중업로드→다른계정로그인</t>
+          <t>승인직전직접이전/후임나감/모임종료</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>작업확인·중단선택·이전계정보호자료비노출</t>
+          <t>버전검증거부·오래된승인미덮어씀</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI32, UI34</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8056,24 +8056,24 @@
       <c r="L112" s="2" t="inlineStr"/>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+          <t>API 권한 + 운영 시나리오 수동</t>
         </is>
       </c>
     </row>
     <row r="113" ht="34" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>TC-F28-04</t>
+          <t>TC-F27-04</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>F28</t>
+          <t>F27</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>저장 공간·캐시·로그아웃·문의</t>
+          <t>방장 부재 수동 복구 (P04)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -8083,17 +8083,17 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>실패문의·공개연락처·저장임시파일</t>
+          <t>복구승인과파일기한/작성자 비교</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>문의식별값·실채널연결·기기쓰기후정리</t>
+          <t>방장역할만변경·기한/소유불변·종료재개불가</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI32, UI34</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
@@ -8111,12 +8111,232 @@
       <c r="L113" s="3" t="inlineStr"/>
       <c r="M113" s="3" t="inlineStr">
         <is>
+          <t>API 권한 + 운영 시나리오 수동</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="34" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TC-F28-01</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>저장 공간·캐시·로그아웃·문의</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>완료원본+예약=5GB경계·동시접수</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>동시초과없음·파생본사용량별도</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>UI03, UI28, UI33, UI35</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>staging 실제연동+실기기/서버경쟁 주입</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>DB 경쟁 + API 통합</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="34" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>TC-F28-02</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>저장 공간·캐시·로그아웃·문의</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>캐시500MB LRU정리·미완료원본포함</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>재생캐시만삭제·유일원본/설명/작업유지</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>UI03, UI28, UI33, UI35</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>staging 실제연동+실기기/서버경쟁 주입</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="inlineStr"/>
+      <c r="K115" s="3" t="inlineStr"/>
+      <c r="L115" s="3" t="inlineStr"/>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
           <t>Android 자동화 + 권한/저장 실기기 수동</t>
         </is>
       </c>
     </row>
+    <row r="116" ht="34" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TC-F28-03</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>저장 공간·캐시·로그아웃·문의</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>로그아웃중업로드→다른계정로그인</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>작업확인·중단선택·이전계정보호자료비노출</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>UI03, UI28, UI33, UI35</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>staging 실제연동+실기기/서버경쟁 주입</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="34" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>TC-F28-04</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>F28</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>저장 공간·캐시·로그아웃·문의</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>실패문의·공개연락처·저장임시파일</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>문의식별값·실채널연결·기기쓰기후정리</t>
+        </is>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>UI03, UI28, UI33, UI35</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>staging 실제연동+실기기/서버경쟁 주입</t>
+        </is>
+      </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+      <c r="J117" s="3" t="inlineStr"/>
+      <c r="K117" s="3" t="inlineStr"/>
+      <c r="L117" s="3" t="inlineStr"/>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>Android 자동화 + 권한/저장 실기기 수동</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M113"/>
+  <autoFilter ref="A1:M117"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
@@ -8129,7 +8349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8652,8 +8872,40 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>CT16</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>모든 현재 참여자의 초대 관리</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>방장/일반 참여자·타인 초대 취소·비참여/탈퇴/퇴장/이용 제한·종료 경합·멱등 재시도</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>현재 참여자 동일 권한·발급자 이력 유지·권한 소멸 뒤 거부·7일/50회/정원 유지</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>API권한+DB경쟁+Android 화면</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F17"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>

--- a/1차 개발 설계서/06 검수 및 추적.xlsx
+++ b/1차 개발 설계서/06 검수 및 추적.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비기능검수" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검수계획" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검증된데모범위" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI통합검수" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'요구사항추적'!$A$1:$G$29</definedName>
@@ -33,6 +34,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'검수계획'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'검증된데모범위'!$A$1:$C$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'검증된데모범위'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'UI통합검수'!$A$1:$D$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'UI통합검수'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +531,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UI01, UI24, UI29, UI35</t>
+          <t>UI01, UI24, UI29, UI35, UI37</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -565,7 +568,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>UI02, UI28, UI30</t>
+          <t>UI02, UI28, UI30, UI36, UI37</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1153,7 +1156,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI16, UI18, UI22, UI28, UI36</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1523,7 +1526,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI03, UI28, UI33, UI35, UI36, UI37</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -1988,7 +1991,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>UI01, UI24, UI29, UI35</t>
+          <t>UI01, UI24, UI29, UI35, UI37</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2043,7 +2046,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>UI01, UI24, UI29, UI35</t>
+          <t>UI01, UI24, UI29, UI35, UI37</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2098,7 +2101,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>UI01, UI24, UI29, UI35</t>
+          <t>UI01, UI24, UI29, UI35, UI37</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2153,7 +2156,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>UI01, UI24, UI29, UI35</t>
+          <t>UI01, UI24, UI29, UI35, UI37</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2208,7 +2211,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>UI02, UI28, UI30</t>
+          <t>UI02, UI28, UI30, UI36, UI37</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2263,7 +2266,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>UI02, UI28, UI30</t>
+          <t>UI02, UI28, UI30, UI36, UI37</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2318,7 +2321,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>UI02, UI28, UI30</t>
+          <t>UI02, UI28, UI30, UI36, UI37</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2373,7 +2376,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>UI02, UI28, UI30</t>
+          <t>UI02, UI28, UI30, UI36, UI37</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -5948,7 +5951,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI16, UI18, UI22, UI28, UI36</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6003,7 +6006,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI16, UI18, UI22, UI28, UI36</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
@@ -6058,7 +6061,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI16, UI18, UI22, UI28, UI36</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6113,7 +6116,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>UI16, UI18, UI22, UI28</t>
+          <t>UI16, UI18, UI22, UI28, UI36</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
@@ -8148,7 +8151,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI03, UI28, UI33, UI35, UI36, UI37</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8203,7 +8206,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI03, UI28, UI33, UI35, UI36, UI37</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
@@ -8258,7 +8261,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI03, UI28, UI33, UI35, UI36, UI37</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -8313,7 +8316,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>UI03, UI28, UI33, UI35</t>
+          <t>UI03, UI28, UI33, UI35, UI36, UI37</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
@@ -9658,4 +9661,313 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>기대 결과</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실제 앱 검수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>U30-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>일반 참여자가 일정의 참여자 목록에서 초대 관리 진입</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>발급·조회·복사·공유·다른 참여자의 초대 취소 가능, 역할 변경은 불가</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>U30-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>초대 화면을 연 뒤 퇴장·이용 제한</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>새 조회/쓰기·이전 요청 재시도 거부, 캐시 링크를 새로 공유하는 동작 차단</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>U30-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>날짜에 방문은 없고 미지정 기록만 있음</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>기록 수 유지, 전체/미지정 경로로 열람 가능</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>U30-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>기간 축소로 기존 기록일이 기간 밖이 됨</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>전체/기간 밖에서 조회, 날짜 필터 범위 이탈 안내, 기록 삭제 없음</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>U30-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>기록 보기 전환·상세 복귀·앱 재실행</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>F16 정렬키·파일 집합·집계 일치, 보기 방식 기억, 영상 소리 정지</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>U30-06</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>길게 선택·버튼 선택·사람별 메뉴·121개 전체 선택</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>모두 같은 선택 흐름, 120개 상한·사진/영상 수·파일별 결과·실패 재시도</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>U30-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>사진4개 완료+1개 예약 후 같은 방문에 추가</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>남은 사진0개, 영상은 별도 계산; 예시10개 한도 미사용</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>U30-08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>마이페이지·계정 닉네임 수정 성공/실패</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>F02 검사·20자 규칙, 동일 소유ID 유지, 서버 성공 전 완료 표시 없음</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>U30-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>설정 초대코드→가입→복귀</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>초대 확인 후 명시적 참여, 실제 상태/정원/기한 재검증</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>U30-10</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>모임에서 나간 사용자의 설정·내 기록</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>공동 조회 불가, 본인 열람/삭제는 유지, 새 저장 불가</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>U30-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>프로필·모임 수·문의·약관 조회 실패</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>예시 프로필/0개/저장 성공 토스트로 대체하지 않고 오류·재시도 표시</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>U30-12</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>방장 기간 수정과 일반 참여자의 직접 요청</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>연속366일·5분·버전·고정 기한 유지, 비방장 거부</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>미실행</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D13"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>